--- a/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
@@ -653,7 +653,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -2023,14 +2023,12 @@
     <row r="42"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="L25:R25"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>
-    <mergeCell ref="H25:K25"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="D4:G8"/>

--- a/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,18 +104,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -132,6 +120,10 @@
       <color rgb="000563C1"/>
       <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -199,25 +191,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -230,7 +215,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,13 +227,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -643,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -657,13 +643,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -674,276 +659,204 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CI&amp;S – Estate Planning &amp; Development (TBC: confirm with Gerard)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Reach and maintain high levels of climate-change resilience maturity</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Maturity assessment of the University’s preparedness for climate-related impacts and capability to respond, assessed across relevant organisational functions:
 o	Governance and strategy
@@ -955,694 +868,671 @@
 o	Financial planning and reporting.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 8a(i), so please include any relevant activity from across 2026.
 Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>8a(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EI1(a)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Evidence of increased maturity of estate and infrastructure planning, development and operations to support the other priority areas in Sustainability 2030</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 7b, so please include any relevant activity from across 2026.
 Case study evidence of increased sustainability maturity in estate and infrastructure planning, development and operations, could include examples of changes to standards, processes, governance, decision-making or project requirements that support Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>We will use case study evidence to show how sustainability maturity is increasing in estate and infrastructure planning, development and operations in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>7b
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>EI1(b)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Estimated sustainability impacts of the University’s estate and infrastructure capital plan to inform progress towards emissions reduction targets and other priority areas (to the extent enabled by available information)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Please provide any available information on sustainability impacts associated with estate and infrastructure projects or capital works relevant to your Faculty/Portfolio. This could include impacts related to emissions and other Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will use estimated sustainability impacts of the capital plan to inform progress reporting towards the emissions reduction target and other priority areas (to the extent information is available).</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr"/>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
+      <c r="I18" s="14" t="inlineStr"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>EI1(c)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Reporting on relevant activities and impacts for the University’s major estate and infrastructure projects and programs aligned with the other priority areas in Sustainability 2030</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Please provide an update on sustainability-related activities and impacts for major estate and infrastructure projects or programs relevant to your Faculty/Portfolio. This could include key initiatives, relevant performance measures and alignment with Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>We will report on sustainability activities and impacts of major estate and infrastructure projects and programs in the Estate and infrastructure section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr"/>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
+      <c r="I19" s="14" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>EI1(d)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Evidence of understanding and integration of Indigenous approaches to sustainability in estate planning and development programs and projects.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>Please provide examples showing how Indigenous approaches, knowledges or perspectives on sustainability have informed estate planning, development programs or projects relevant to your Faculty/Portfolio. This could include how Indigenous stakeholders were engaged and what changed as a result.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>We will report on how Indigenous approaches to sustainability are informing estate planning and development, with examples where permission to share is confirmed.</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr"/>
-      <c r="J20" s="19" t="inlineStr"/>
-      <c r="K20" s="19" t="inlineStr"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
+      <c r="I20" s="14" t="inlineStr"/>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
     </row>
     <row r="21"/>
     <row r="23">
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>CI&amp;S – Sustainability Strategy (incl. CLLAP)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O26" s="15" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P26" s="15" t="inlineStr">
+      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q26" s="15" t="inlineStr">
+      <c r="P26" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R26" s="15" t="inlineStr">
+      <c r="Q26" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="16" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr"/>
-      <c r="I27" s="16" t="inlineStr"/>
-      <c r="J27" s="16" t="inlineStr"/>
-      <c r="K27" s="16" t="inlineStr"/>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O27" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P27" s="16" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q27" s="16" t="inlineStr">
+      <c r="P27" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R27" s="16" t="inlineStr">
+      <c r="Q27" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr"/>
-      <c r="J28" s="19" t="inlineStr"/>
-      <c r="K28" s="19" t="inlineStr"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
-      <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="n"/>
+      <c r="I28" s="14" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="16" t="n"/>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr"/>
-      <c r="J29" s="19" t="inlineStr"/>
-      <c r="K29" s="19" t="inlineStr"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
-      <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="21" t="n"/>
+      <c r="I29" s="14" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="16" t="n"/>
     </row>
     <row r="30" ht="150" customHeight="1">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and co curricular learning (eg Wattle Fellowship; Melbourne Plus)</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr"/>
-      <c r="J30" s="19" t="inlineStr"/>
-      <c r="K30" s="19" t="inlineStr"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
-      <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="21" t="n"/>
+      <c r="I30" s="14" t="inlineStr"/>
+      <c r="J30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="inlineStr"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
     </row>
     <row r="31" ht="150" customHeight="1">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 5a(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 5a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of researchers within your Faculty/Portfolio contributing to University operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support. Briefly describe the operational challenge, researcher contribution and resulting or expected outcome.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="15" t="inlineStr">
         <is>
           <t>5a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
-      <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="21" t="n"/>
-      <c r="R31" s="21" t="n"/>
+      <c r="K31" s="14" t="inlineStr"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="16" t="n"/>
+      <c r="Q31" s="16" t="n"/>
     </row>
     <row r="32" ht="150" customHeight="1">
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio demonstrating how research has contributed to meaningful sustainability outcomes. Briefly describe the research, stakeholders involved, pathway to impact and evidence of the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr"/>
-      <c r="J32" s="19" t="inlineStr"/>
-      <c r="K32" s="19" t="inlineStr"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
-      <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="21" t="n"/>
+      <c r="I32" s="14" t="inlineStr"/>
+      <c r="J32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="inlineStr"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="16" t="n"/>
     </row>
     <row r="33" ht="150" customHeight="1">
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr"/>
-      <c r="J33" s="19" t="inlineStr"/>
-      <c r="K33" s="19" t="inlineStr"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
-      <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="21" t="n"/>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="16" t="n"/>
     </row>
     <row r="34" ht="150" customHeight="1">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>CL1(c)</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Achieve net zero emissions by 2050:
 Interim target
@@ -1653,400 +1543,381 @@
 Reduce emissions by 90% across all emissions scopes by CY2050 on the CY2023 re-baseline and invest in carbon removal credits for residual emissions from hard-to-abate sources (up to 10%).</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Review of Climate Leadership targets by 2030.[2]</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>For internal planning: we will record the status of the planned review of Climate Leadership targets (due by 2030).</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I34" s="19" t="inlineStr"/>
-      <c r="J34" s="19" t="inlineStr"/>
-      <c r="K34" s="19" t="inlineStr"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
+      <c r="I34" s="14" t="inlineStr"/>
+      <c r="J34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="inlineStr"/>
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="16" t="n"/>
     </row>
     <row r="35" ht="150" customHeight="1">
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>AI1(a)</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Established measurement of estimated operational impacts and opportunities (eg operational impacts could include energy, water, emissions and intensity measures)</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr"/>
-      <c r="J35" s="19" t="inlineStr"/>
-      <c r="K35" s="19" t="inlineStr"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
-      <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="21" t="n"/>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="16" t="n"/>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="16" t="n"/>
     </row>
     <row r="36" ht="150" customHeight="1">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>AI1(b)</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Case studies of sustainability and AI-related education, research and collaboration activities.</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr"/>
-      <c r="J36" s="19" t="inlineStr"/>
-      <c r="K36" s="19" t="inlineStr"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
-      <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="21" t="n"/>
+      <c r="I36" s="14" t="inlineStr"/>
+      <c r="J36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="16" t="n"/>
+      <c r="Q36" s="16" t="n"/>
     </row>
     <row r="37" ht="150" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Modern slavery and human rights</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 11c(ii), so please include any relevant activity from across 2026.
 Annual Modern Slavery Statement, with case studies</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
         <is>
           <t>11c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr"/>
-      <c r="J37" s="19" t="inlineStr"/>
-      <c r="K37" s="19" t="inlineStr"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
-      <c r="P37" s="21" t="n"/>
-      <c r="Q37" s="21" t="n"/>
-      <c r="R37" s="21" t="n"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="16" t="n"/>
+      <c r="M37" s="16" t="n"/>
+      <c r="N37" s="16" t="n"/>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="16" t="n"/>
+      <c r="Q37" s="16" t="n"/>
     </row>
     <row r="38" ht="150" customHeight="1">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 12b(i), so please include any relevant activity from across 2026.
 Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="G38" s="19" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I38" s="19" t="inlineStr"/>
-      <c r="J38" s="19" t="inlineStr"/>
-      <c r="K38" s="19" t="inlineStr"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
-      <c r="P38" s="21" t="n"/>
-      <c r="Q38" s="21" t="n"/>
-      <c r="R38" s="21" t="n"/>
+      <c r="I38" s="14" t="inlineStr"/>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="16" t="n"/>
+      <c r="M38" s="16" t="n"/>
+      <c r="N38" s="16" t="n"/>
+      <c r="O38" s="16" t="n"/>
+      <c r="P38" s="16" t="n"/>
+      <c r="Q38" s="16" t="n"/>
     </row>
     <row r="39" ht="150" customHeight="1">
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 2a, so please include any relevant activity from across 2026.
 Please comment on sustainability-related living labs in your area – their activities, outputs, outcomes and impact.
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr"/>
-      <c r="J39" s="19" t="inlineStr"/>
-      <c r="K39" s="19" t="inlineStr"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="21" t="n"/>
-      <c r="P39" s="21" t="n"/>
-      <c r="Q39" s="21" t="n"/>
-      <c r="R39" s="21" t="n"/>
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="16" t="n"/>
+      <c r="M39" s="16" t="n"/>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="16" t="n"/>
+      <c r="P39" s="16" t="n"/>
+      <c r="Q39" s="16" t="n"/>
     </row>
     <row r="40" ht="150" customHeight="1">
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr"/>
-      <c r="J40" s="19" t="inlineStr"/>
-      <c r="K40" s="19" t="inlineStr"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="21" t="n"/>
-      <c r="P40" s="21" t="n"/>
-      <c r="Q40" s="21" t="n"/>
-      <c r="R40" s="21" t="n"/>
+      <c r="I40" s="14" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="16" t="n"/>
+      <c r="M40" s="16" t="n"/>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="16" t="n"/>
+      <c r="P40" s="16" t="n"/>
+      <c r="Q40" s="16" t="n"/>
     </row>
     <row r="41" ht="150" customHeight="1">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr"/>
-      <c r="J41" s="19" t="inlineStr"/>
-      <c r="K41" s="19" t="inlineStr"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="21" t="n"/>
-      <c r="P41" s="21" t="n"/>
-      <c r="Q41" s="21" t="n"/>
-      <c r="R41" s="21" t="n"/>
+      <c r="I41" s="14" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="16" t="n"/>
+      <c r="M41" s="16" t="n"/>
+      <c r="N41" s="16" t="n"/>
+      <c r="O41" s="16" t="n"/>
+      <c r="P41" s="16" t="n"/>
+      <c r="Q41" s="16" t="n"/>
     </row>
     <row r="42"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="11">
-    <mergeCell ref="L25:R25"/>
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="6">
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
+    <mergeCell ref="L25:Q25"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="L16:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="P16:P20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation sqref="L28:L41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q28:Q41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+    <dataValidation sqref="P28:P41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2091,7 +1962,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -2103,12 +1974,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -2116,77 +1987,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -2237,693 +2108,693 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>CD Development &amp; Estate Planning teams</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>7b</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University has led or influenced discussions with precinct partners to further precinct-specific approaches to sustainability</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Case studies identifying the nature of the University’s involvement in sustainability issues for each precinct.</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr"/>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>EI1(a)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Case studies demonstrating climate change preparedness activities in the Portfolio</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>9a(i)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Each campus achieves no net loss of biodiversity relative to defined baseline years by 2025</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Describe the impact of initiatives and projects (including the Estate Master Plan) on biodiversity</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>10a(i)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>The University has reduced total water consumption by 10% relative to a 2019 baseline</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Describe efforts to reduce water use in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>10b(i)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>The University has significantly increased the proportion of water consumption from non-potable sources compared to a 2019 baseline</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Describe efforts to increase non-potable water consumption in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr"/>
-      <c r="G12" s="19" t="inlineStr"/>
-      <c r="H12" s="19" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>11a(i)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Describe efforts to reduce and more effectively manage waste in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr"/>
-      <c r="G13" s="19" t="inlineStr"/>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>11a(ii)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr"/>
-      <c r="G14" s="19" t="inlineStr"/>
-      <c r="H14" s="19" t="inlineStr"/>
-      <c r="I14" s="19" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>CD Sustainability Strategy</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="160" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions
 % change in air travel emissions in the Portfolio</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Data request sent</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>The University has met its target of reducing flight emissions by 10%. Total GHG emissions in 2025 from flights was estimated to be 20,052 tCO2e whilst 2019 flight emissions were 27,044 tCO2e; approximately a 26% reduction in absolute emissions. 
 In terms of total distance flown, the University staff travelled 115,416,715 air kilometres in 2025; a 13% reduction compared with the 132,329,019 air kilometres flown in 2019.
 This achievement is attributable in part to  the "Air Travel Emissions Reduction Program", reduced travel budgets across the University, as well as improvements within the aviation industry such as newer fuel efficient air craft models being integrated into global fleets and lower carbon fuels being used.</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="160" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>1a(iI)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Progress towards attaining Climate Active carbon neutral certification</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Registered with Climate Active. Should be going ahead as planned.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>The University is currently on track to being Climate Active Carbon Neutral certified for its 2025 Carbon Footprint. The University will be undergoing an assurance and technical assessment of its 2025 GHG inventory to as per Climate Active requirements, after which it submit all required document for certification. Notably, there can be a delay between the time of submission and actual approval of certification. The University will provide updates on this process as they become relevant.</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr"/>
-      <c r="I19" s="19" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="160" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>1a(iii)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Case studies and other knowledge mobilisation activities that enable 
 others to implement ambitious climate action</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>100% renewables - main story
 Supplier participation in providing data - reducing reported emissions based on actual emissions - mini case study. SBTI requirement into Keypath - option for case study [now working with suppliers to set 1.5 degree targets] - workshop with CD</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr"/>
-      <c r="H20" s="19" t="inlineStr"/>
-      <c r="I20" s="19" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="160" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Report on living labs at the University - outputs, outcomes and impact.</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr"/>
-      <c r="G21" s="19" t="inlineStr"/>
-      <c r="H21" s="19" t="inlineStr"/>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="160" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>4b(ii)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Report on Mark Latham's project - as an example of a measure developed</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr"/>
-      <c r="G22" s="19" t="inlineStr"/>
-      <c r="H22" s="19" t="inlineStr"/>
-      <c r="I22" s="19" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="160" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>5a(ii)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Sustainability research is integrated with campus operations and planning, to be an international exemplar of a sustainable community</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Percentage of the University's research outputs that map to one or more SDGs in the top 10 per cent most cited in their field; Number of patent, policy and news/social media mentions for University research outputs mapped to SDGs</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr"/>
-      <c r="H23" s="19" t="inlineStr"/>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="160" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr"/>
-      <c r="G24" s="19" t="inlineStr"/>
-      <c r="H24" s="19" t="inlineStr"/>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr"/>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="160" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr"/>
-      <c r="G25" s="19" t="inlineStr"/>
-      <c r="H25" s="19" t="inlineStr"/>
-      <c r="I25" s="19" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="160" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>11c(ii)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>List of Fair Trade and other relevant third-party certifications</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr"/>
-      <c r="G26" s="19" t="inlineStr"/>
-      <c r="H26" s="19" t="inlineStr"/>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr"/>
+      <c r="G26" s="14" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr"/>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>12b(i)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr"/>
-      <c r="G27" s="19" t="inlineStr"/>
-      <c r="H27" s="19" t="inlineStr"/>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="160" customHeight="1">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>12b(ii)</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Reporting on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr"/>
-      <c r="G28" s="19" t="inlineStr"/>
-      <c r="H28" s="19" t="inlineStr"/>
-      <c r="I28" s="19" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="160" customHeight="1">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>11a(ii)</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects (Gerard to supply for major projects)</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr"/>
-      <c r="G29" s="19" t="inlineStr"/>
-      <c r="H29" s="19" t="inlineStr"/>
-      <c r="I29" s="19" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2981,427 +2852,427 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr"/>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="27" t="inlineStr"/>
-      <c r="F7" s="27" t="inlineStr"/>
-      <c r="G7" s="27" t="inlineStr"/>
-      <c r="H7" s="27" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr"/>
-      <c r="J7" s="27" t="inlineStr"/>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr"/>
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="23" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr"/>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Maturity assessment of the University's preparedness for climate-related impacts and capability to respond</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Average Total Maturity Score</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="28" t="inlineStr"/>
-      <c r="K8" s="30" t="n"/>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="30" t="n"/>
-      <c r="N8" s="30" t="n"/>
-      <c r="O8" s="30" t="n"/>
+      <c r="E8" s="24" t="inlineStr"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="24" t="inlineStr"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="n"/>
+      <c r="O8" s="26" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Maturitu Score - Governance and strategy</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="32" t="n"/>
-      <c r="G9" s="32" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="32" t="n"/>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="19" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="31" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Health and safety</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="32" t="n"/>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="19" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Business continuity</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="19" t="n"/>
-      <c r="N11" s="19" t="n"/>
-      <c r="O11" s="19" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr"/>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Emergency management and critical incidence management</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Estate and buildings</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="19" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr"/>
-      <c r="D14" s="31" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Water management</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K14" s="19" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="19" t="n"/>
-      <c r="N14" s="19" t="n"/>
-      <c r="O14" s="19" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Maturity Score - Financial planning and reporting</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="19" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Number of projects funded (CLLAP)</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr"/>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Total funding for projects</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K17" s="19" t="n"/>
-      <c r="L17" s="19" t="n"/>
-      <c r="M17" s="19" t="n"/>
-      <c r="N17" s="19" t="n"/>
-      <c r="O17" s="19" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -3425,13 +3296,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3447,21 +3318,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -3486,24 +3342,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -3519,24 +3359,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -3552,47 +3376,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -3600,11 +3392,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - SR26 sustainability reporting request.xlsx
@@ -23,21 +23,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -191,77 +183,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,32 +641,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -692,171 +672,174 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>CI&amp;S – Estate Planning &amp; Development (TBC: confirm with Gerard)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="204" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Reach and maintain high levels of climate-change resilience maturity</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Maturity assessment of the University’s preparedness for climate-related impacts and capability to respond, assessed across relevant organisational functions:
 o	Governance and strategy
@@ -868,671 +851,673 @@
 o	Financial planning and reporting.</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 8a(i), so please include any relevant activity from across 2026.
 Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>8a(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="171" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EI1(a)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Evidence of increased maturity of estate and infrastructure planning, development and operations to support the other priority areas in Sustainability 2030</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 7b, so please include any relevant activity from across 2026.
 Case study evidence of increased sustainability maturity in estate and infrastructure planning, development and operations, could include examples of changes to standards, processes, governance, decision-making or project requirements that support Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>We will use case study evidence to show how sustainability maturity is increasing in estate and infrastructure planning, development and operations in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>7b
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>EI1(b)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Estimated sustainability impacts of the University’s estate and infrastructure capital plan to inform progress towards emissions reduction targets and other priority areas (to the extent enabled by available information)</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Please provide any available information on sustainability impacts associated with estate and infrastructure projects or capital works relevant to your Faculty/Portfolio. This could include impacts related to emissions and other Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will use estimated sustainability impacts of the capital plan to inform progress reporting towards the emissions reduction target and other priority areas (to the extent information is available).</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
+      <c r="I18" s="12" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>EI1(c)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Reporting on relevant activities and impacts for the University’s major estate and infrastructure projects and programs aligned with the other priority areas in Sustainability 2030</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Please provide an update on sustainability-related activities and impacts for major estate and infrastructure projects or programs relevant to your Faculty/Portfolio. This could include key initiatives, relevant performance measures and alignment with Sustainability 2030 priority areas.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>We will report on sustainability activities and impacts of major estate and infrastructure projects and programs in the Estate and infrastructure section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr"/>
-      <c r="J19" s="14" t="inlineStr"/>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
+      <c r="I19" s="12" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>EI1(d)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Estate and infrastructure</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Integrate environmental sustainability in the way that the University achieves strategic and operational objectives for our estate and infrastructure.</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Evidence of understanding and integration of Indigenous approaches to sustainability in estate planning and development programs and projects.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Please provide examples showing how Indigenous approaches, knowledges or perspectives on sustainability have informed estate planning, development programs or projects relevant to your Faculty/Portfolio. This could include how Indigenous stakeholders were engaged and what changed as a result.</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>We will report on how Indigenous approaches to sustainability are informing estate planning and development, with examples where permission to share is confirmed.</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
     </row>
     <row r="21"/>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23" ht="39" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>CI&amp;S – Sustainability Strategy (incl. CLLAP)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="7" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="27" customHeight="1">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O26" s="10" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P26" s="10" t="inlineStr">
+      <c r="P26" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr"/>
-      <c r="C27" s="11" t="inlineStr"/>
-      <c r="D27" s="11" t="inlineStr"/>
-      <c r="E27" s="11" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="11" t="inlineStr"/>
-      <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="11" t="inlineStr"/>
-      <c r="L27" s="11" t="inlineStr">
+    <row r="27" ht="81" customHeight="1">
+      <c r="B27" s="9" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P27" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q27" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr"/>
-      <c r="J28" s="14" t="inlineStr"/>
-      <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
+      <c r="I28" s="12" t="inlineStr"/>
+      <c r="J28" s="12" t="inlineStr"/>
+      <c r="K28" s="12" t="inlineStr"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="14" t="n"/>
+      <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14" t="n"/>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr"/>
-      <c r="J29" s="14" t="inlineStr"/>
-      <c r="K29" s="14" t="inlineStr"/>
-      <c r="L29" s="16" t="n"/>
-      <c r="M29" s="16" t="n"/>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16" t="n"/>
-      <c r="P29" s="16" t="n"/>
-      <c r="Q29" s="16" t="n"/>
+      <c r="I29" s="12" t="inlineStr"/>
+      <c r="J29" s="12" t="inlineStr"/>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="14" t="n"/>
+      <c r="Q29" s="14" t="n"/>
     </row>
     <row r="30" ht="150" customHeight="1">
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and co curricular learning (eg Wattle Fellowship; Melbourne Plus)</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="14" t="inlineStr"/>
-      <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="16" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16" t="n"/>
-      <c r="P30" s="16" t="n"/>
-      <c r="Q30" s="16" t="n"/>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="B31" s="12" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr"/>
+      <c r="J30" s="12" t="inlineStr"/>
+      <c r="K30" s="12" t="inlineStr"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
+      <c r="O30" s="14" t="n"/>
+      <c r="P30" s="14" t="n"/>
+      <c r="Q30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="220" customHeight="1">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 5a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of researchers within your Faculty/Portfolio contributing to University operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support. Briefly describe the operational challenge, researcher contribution and resulting or expected outcome.</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H31" s="15" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>5a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr"/>
-      <c r="L31" s="16" t="n"/>
-      <c r="M31" s="16" t="n"/>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="16" t="n"/>
-      <c r="P31" s="16" t="n"/>
-      <c r="Q31" s="16" t="n"/>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="14" t="n"/>
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="14" t="n"/>
+      <c r="Q31" s="14" t="n"/>
     </row>
     <row r="32" ht="150" customHeight="1">
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio demonstrating how research has contributed to meaningful sustainability outcomes. Briefly describe the research, stakeholders involved, pathway to impact and evidence of the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr"/>
-      <c r="J32" s="14" t="inlineStr"/>
-      <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="16" t="n"/>
-      <c r="M32" s="16" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="12" t="inlineStr"/>
+      <c r="K32" s="12" t="inlineStr"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
+      <c r="O32" s="14" t="n"/>
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="n"/>
     </row>
     <row r="33" ht="150" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr"/>
-      <c r="J33" s="14" t="inlineStr"/>
-      <c r="K33" s="14" t="inlineStr"/>
-      <c r="L33" s="16" t="n"/>
-      <c r="M33" s="16" t="n"/>
-      <c r="N33" s="16" t="n"/>
-      <c r="O33" s="16" t="n"/>
-      <c r="P33" s="16" t="n"/>
-      <c r="Q33" s="16" t="n"/>
-    </row>
-    <row r="34" ht="150" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr"/>
+      <c r="J33" s="12" t="inlineStr"/>
+      <c r="K33" s="12" t="inlineStr"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="14" t="n"/>
+      <c r="P33" s="14" t="n"/>
+      <c r="Q33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="220" customHeight="1">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>CL1(c)</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Achieve net zero emissions by 2050:
 Interim target
@@ -1543,364 +1528,364 @@
 Reduce emissions by 90% across all emissions scopes by CY2050 on the CY2023 re-baseline and invest in carbon removal credits for residual emissions from hard-to-abate sources (up to 10%).</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Review of Climate Leadership targets by 2030.[2]</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>For internal planning: we will record the status of the planned review of Climate Leadership targets (due by 2030).</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr"/>
-      <c r="J34" s="14" t="inlineStr"/>
-      <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="16" t="n"/>
-      <c r="M34" s="16" t="n"/>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="16" t="n"/>
-      <c r="P34" s="16" t="n"/>
-      <c r="Q34" s="16" t="n"/>
+      <c r="I34" s="12" t="inlineStr"/>
+      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="12" t="inlineStr"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14" t="n"/>
     </row>
     <row r="35" ht="150" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>AI1(a)</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Established measurement of estimated operational impacts and opportunities (eg operational impacts could include energy, water, emissions and intensity measures)</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr"/>
-      <c r="J35" s="14" t="inlineStr"/>
-      <c r="K35" s="14" t="inlineStr"/>
-      <c r="L35" s="16" t="n"/>
-      <c r="M35" s="16" t="n"/>
-      <c r="N35" s="16" t="n"/>
-      <c r="O35" s="16" t="n"/>
-      <c r="P35" s="16" t="n"/>
-      <c r="Q35" s="16" t="n"/>
+      <c r="I35" s="12" t="inlineStr"/>
+      <c r="J35" s="12" t="inlineStr"/>
+      <c r="K35" s="12" t="inlineStr"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14" t="n"/>
+      <c r="O35" s="14" t="n"/>
+      <c r="P35" s="14" t="n"/>
+      <c r="Q35" s="14" t="n"/>
     </row>
     <row r="36" ht="150" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>AI1(b)</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Case studies of sustainability and AI-related education, research and collaboration activities.</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr"/>
-      <c r="J36" s="14" t="inlineStr"/>
-      <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="16" t="n"/>
-      <c r="P36" s="16" t="n"/>
-      <c r="Q36" s="16" t="n"/>
+      <c r="I36" s="12" t="inlineStr"/>
+      <c r="J36" s="12" t="inlineStr"/>
+      <c r="K36" s="12" t="inlineStr"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14" t="n"/>
+      <c r="O36" s="14" t="n"/>
+      <c r="P36" s="14" t="n"/>
+      <c r="Q36" s="14" t="n"/>
     </row>
     <row r="37" ht="150" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Modern slavery and human rights</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 11c(ii), so please include any relevant activity from across 2026.
 Annual Modern Slavery Statement, with case studies</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H37" s="15" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>11c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr"/>
-      <c r="J37" s="14" t="inlineStr"/>
-      <c r="K37" s="14" t="inlineStr"/>
-      <c r="L37" s="16" t="n"/>
-      <c r="M37" s="16" t="n"/>
-      <c r="N37" s="16" t="n"/>
-      <c r="O37" s="16" t="n"/>
-      <c r="P37" s="16" t="n"/>
-      <c r="Q37" s="16" t="n"/>
+      <c r="I37" s="12" t="inlineStr"/>
+      <c r="J37" s="12" t="inlineStr"/>
+      <c r="K37" s="12" t="inlineStr"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="14" t="n"/>
+      <c r="P37" s="14" t="n"/>
+      <c r="Q37" s="14" t="n"/>
     </row>
     <row r="38" ht="150" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 12b(i), so please include any relevant activity from across 2026.
 Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr"/>
-      <c r="J38" s="14" t="inlineStr"/>
-      <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="16" t="n"/>
-      <c r="M38" s="16" t="n"/>
-      <c r="N38" s="16" t="n"/>
-      <c r="O38" s="16" t="n"/>
-      <c r="P38" s="16" t="n"/>
-      <c r="Q38" s="16" t="n"/>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="B39" s="12" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr"/>
+      <c r="J38" s="12" t="inlineStr"/>
+      <c r="K38" s="12" t="inlineStr"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
+      <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="171" customHeight="1">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 2a, so please include any relevant activity from across 2026.
 Please comment on sustainability-related living labs in your area – their activities, outputs, outcomes and impact.
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H39" s="15" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr"/>
-      <c r="J39" s="14" t="inlineStr"/>
-      <c r="K39" s="14" t="inlineStr"/>
-      <c r="L39" s="16" t="n"/>
-      <c r="M39" s="16" t="n"/>
-      <c r="N39" s="16" t="n"/>
-      <c r="O39" s="16" t="n"/>
-      <c r="P39" s="16" t="n"/>
-      <c r="Q39" s="16" t="n"/>
+      <c r="I39" s="12" t="inlineStr"/>
+      <c r="J39" s="12" t="inlineStr"/>
+      <c r="K39" s="12" t="inlineStr"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14" t="n"/>
+      <c r="O39" s="14" t="n"/>
+      <c r="P39" s="14" t="n"/>
+      <c r="Q39" s="14" t="n"/>
     </row>
     <row r="40" ht="150" customHeight="1">
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr"/>
-      <c r="J40" s="14" t="inlineStr"/>
-      <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="16" t="n"/>
-      <c r="M40" s="16" t="n"/>
-      <c r="N40" s="16" t="n"/>
-      <c r="O40" s="16" t="n"/>
-      <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="16" t="n"/>
+      <c r="I40" s="12" t="inlineStr"/>
+      <c r="J40" s="12" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14" t="n"/>
+      <c r="O40" s="14" t="n"/>
+      <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="14" t="n"/>
     </row>
     <row r="41" ht="150" customHeight="1">
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr"/>
-      <c r="J41" s="14" t="inlineStr"/>
-      <c r="K41" s="14" t="inlineStr"/>
-      <c r="L41" s="16" t="n"/>
-      <c r="M41" s="16" t="n"/>
-      <c r="N41" s="16" t="n"/>
-      <c r="O41" s="16" t="n"/>
-      <c r="P41" s="16" t="n"/>
-      <c r="Q41" s="16" t="n"/>
+      <c r="I41" s="12" t="inlineStr"/>
+      <c r="J41" s="12" t="inlineStr"/>
+      <c r="K41" s="12" t="inlineStr"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="n"/>
     </row>
     <row r="42"/>
   </sheetData>
@@ -1954,110 +1939,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -2088,713 +2065,703 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Commercial, Infrastructure &amp; Sustainability (CI&amp;S)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>CD Development &amp; Estate Planning teams</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>7b</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University has led or influenced discussions with precinct partners to further precinct-specific approaches to sustainability</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Case studies identifying the nature of the University’s involvement in sustainability issues for each precinct.</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>EI1(a)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Case studies demonstrating climate change preparedness activities in the Portfolio</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>9a(i)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Each campus achieves no net loss of biodiversity relative to defined baseline years by 2025</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Describe the impact of initiatives and projects (including the Estate Master Plan) on biodiversity</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>10a(i)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>The University has reduced total water consumption by 10% relative to a 2019 baseline</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Describe efforts to reduce water use in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="12" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>10b(i)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>The University has significantly increased the proportion of water consumption from non-potable sources compared to a 2019 baseline</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Describe efforts to increase non-potable water consumption in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr"/>
+      <c r="G12" s="12" t="inlineStr"/>
+      <c r="H12" s="12" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>11a(i)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Describe efforts to reduce and more effectively manage waste in development projects and estate planning activities</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="12" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>11a(ii)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr"/>
-      <c r="G14" s="14" t="inlineStr"/>
-      <c r="H14" s="14" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="22" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr"/>
+      <c r="G14" s="12" t="inlineStr"/>
+      <c r="H14" s="12" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>CD Sustainability Strategy</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+    <row r="17" ht="42" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="160" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+    <row r="18" ht="237" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions
 % change in air travel emissions in the Portfolio</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Data request sent</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>The University has met its target of reducing flight emissions by 10%. Total GHG emissions in 2025 from flights was estimated to be 20,052 tCO2e whilst 2019 flight emissions were 27,044 tCO2e; approximately a 26% reduction in absolute emissions. 
 In terms of total distance flown, the University staff travelled 115,416,715 air kilometres in 2025; a 13% reduction compared with the 132,329,019 air kilometres flown in 2019.
 This achievement is attributable in part to  the "Air Travel Emissions Reduction Program", reduced travel budgets across the University, as well as improvements within the aviation industry such as newer fuel efficient air craft models being integrated into global fleets and lower carbon fuels being used.</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="160" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>1a(iI)</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Progress towards attaining Climate Active carbon neutral certification</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Registered with Climate Active. Should be going ahead as planned.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>The University is currently on track to being Climate Active Carbon Neutral certified for its 2025 Carbon Footprint. The University will be undergoing an assurance and technical assessment of its 2025 GHG inventory to as per Climate Active requirements, after which it submit all required document for certification. Notably, there can be a delay between the time of submission and actual approval of certification. The University will provide updates on this process as they become relevant.</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="160" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>1a(iii)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"> Case studies and other knowledge mobilisation activities that enable 
 others to implement ambitious climate action</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>100% renewables - main story
 Supplier participation in providing data - reducing reported emissions based on actual emissions - mini case study. SBTI requirement into Keypath - option for case study [now working with suppliers to set 1.5 degree targets] - workshop with CD</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr"/>
-      <c r="H20" s="14" t="inlineStr"/>
-      <c r="I20" s="14" t="inlineStr"/>
+      <c r="G20" s="12" t="inlineStr"/>
+      <c r="H20" s="12" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="160" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Report on living labs at the University - outputs, outcomes and impact.</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr"/>
-      <c r="G21" s="14" t="inlineStr"/>
-      <c r="H21" s="14" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="12" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="160" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>4b(ii)</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Report on Mark Latham's project - as an example of a measure developed</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr"/>
-      <c r="G22" s="14" t="inlineStr"/>
-      <c r="H22" s="14" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="160" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>5a(ii)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Sustainability research is integrated with campus operations and planning, to be an international exemplar of a sustainable community</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Percentage of the University's research outputs that map to one or more SDGs in the top 10 per cent most cited in their field; Number of patent, policy and news/social media mentions for University research outputs mapped to SDGs</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr"/>
-      <c r="H23" s="14" t="inlineStr"/>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="160" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr"/>
-      <c r="G24" s="14" t="inlineStr"/>
-      <c r="H24" s="14" t="inlineStr"/>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr"/>
+      <c r="G24" s="12" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr"/>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="160" customHeight="1">
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr"/>
-      <c r="G25" s="14" t="inlineStr"/>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr"/>
+      <c r="I25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="160" customHeight="1">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>11c(ii)</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>List of Fair Trade and other relevant third-party certifications</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr"/>
-      <c r="G26" s="14" t="inlineStr"/>
-      <c r="H26" s="14" t="inlineStr"/>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr"/>
+      <c r="H26" s="12" t="inlineStr"/>
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>12b(i)</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr"/>
-      <c r="G27" s="14" t="inlineStr"/>
-      <c r="H27" s="14" t="inlineStr"/>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr"/>
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="160" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>12b(ii)</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Reporting on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr"/>
-      <c r="G28" s="14" t="inlineStr"/>
-      <c r="H28" s="14" t="inlineStr"/>
-      <c r="I28" s="14" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr"/>
+      <c r="G28" s="12" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr"/>
+      <c r="I28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="160" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>11a(ii)</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects (Gerard to supply for major projects)</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr"/>
-      <c r="G29" s="14" t="inlineStr"/>
-      <c r="H29" s="14" t="inlineStr"/>
-      <c r="I29" s="14" t="inlineStr"/>
+      <c r="F29" s="12" t="inlineStr"/>
+      <c r="G29" s="12" t="inlineStr"/>
+      <c r="H29" s="12" t="inlineStr"/>
+      <c r="I29" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2816,6 +2783,7 @@
   <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -2832,447 +2800,437 @@
     <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2026 target status assessment and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Quantitative data – Commercial, Infrastructure &amp; Sustainability (CI&amp;S)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="27" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr"/>
-      <c r="E7" s="23" t="inlineStr"/>
-      <c r="F7" s="23" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="24" t="inlineStr">
+    <row r="8" ht="72" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Maturity assessment of the University's preparedness for climate-related impacts and capability to respond</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Average Total Maturity Score</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr"/>
-      <c r="F8" s="25" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="24" t="inlineStr"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="26" t="n"/>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="26" t="n"/>
-      <c r="O8" s="26" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="22" t="inlineStr"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Maturitu Score - Governance and strategy</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Health and safety</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
-      <c r="O10" s="14" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Business continuity</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Emergency management and critical incidence management</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="14" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Estate and buildings</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
-      <c r="N13" s="14" t="n"/>
-      <c r="O13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="39" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr"/>
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Water management</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="26" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="26" t="n"/>
+      <c r="I14" s="26" t="n"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="14" t="n"/>
-      <c r="N14" s="14" t="n"/>
-      <c r="O14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Maturity Score - Financial planning and reporting</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="14" t="n"/>
-      <c r="O15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Number of projects funded (CLLAP)</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
+      <c r="H16" s="26" t="n"/>
+      <c r="I16" s="26" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="39" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Total funding for projects</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="n"/>
+      <c r="H17" s="26" t="n"/>
+      <c r="I17" s="26" t="n"/>
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -3296,10 +3254,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -3321,7 +3286,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -3343,7 +3308,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -3360,7 +3325,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -3377,35 +3342,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>
